--- a/public/templates/food&Infant/XLSX-Food&InfantHeader.xlsx
+++ b/public/templates/food&Infant/XLSX-Food&InfantHeader.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="7" rupBuild="9302"/>
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -223,9 +223,6 @@
     <t>India</t>
   </si>
   <si>
-    <t>Veg</t>
-  </si>
-  <si>
     <t>Kilogram (kg)</t>
   </si>
   <si>
@@ -770,6 +767,9 @@
   </si>
   <si>
     <t>as-per-label</t>
+  </si>
+  <si>
+    <t>veg</t>
   </si>
 </sst>
 </file>
@@ -996,11 +996,19 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1014,14 +1022,6 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1325,7 +1325,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1344,203 +1344,203 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:68" x14ac:dyDescent="0.3">
-      <c r="A1" s="37" t="s">
+      <c r="A1" s="38" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="36" t="s">
+      <c r="B1" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="37" t="s">
+      <c r="C1" s="38" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="37" t="s">
+      <c r="D1" s="38" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="37" t="s">
+      <c r="E1" s="38" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="36" t="s">
+      <c r="F1" s="39" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="37" t="s">
+      <c r="G1" s="38" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="37" t="s">
+      <c r="H1" s="38" t="s">
         <v>40</v>
       </c>
-      <c r="I1" s="37" t="s">
+      <c r="I1" s="38" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="37" t="s">
+      <c r="J1" s="38" t="s">
         <v>41</v>
       </c>
-      <c r="K1" s="37" t="s">
+      <c r="K1" s="38" t="s">
         <v>8</v>
       </c>
-      <c r="L1" s="37" t="s">
+      <c r="L1" s="38" t="s">
         <v>9</v>
       </c>
-      <c r="M1" s="37" t="s">
+      <c r="M1" s="38" t="s">
         <v>10</v>
       </c>
-      <c r="N1" s="37" t="s">
+      <c r="N1" s="38" t="s">
         <v>11</v>
       </c>
-      <c r="O1" s="37" t="s">
+      <c r="O1" s="38" t="s">
         <v>12</v>
       </c>
-      <c r="P1" s="37" t="s">
+      <c r="P1" s="38" t="s">
         <v>13</v>
       </c>
-      <c r="Q1" s="37" t="s">
+      <c r="Q1" s="38" t="s">
         <v>14</v>
       </c>
-      <c r="R1" s="37" t="s">
+      <c r="R1" s="38" t="s">
         <v>15</v>
       </c>
-      <c r="S1" s="37" t="s">
+      <c r="S1" s="38" t="s">
         <v>16</v>
       </c>
-      <c r="T1" s="37" t="s">
+      <c r="T1" s="38" t="s">
         <v>17</v>
       </c>
-      <c r="U1" s="37" t="s">
+      <c r="U1" s="38" t="s">
         <v>18</v>
       </c>
-      <c r="V1" s="37" t="s">
+      <c r="V1" s="38" t="s">
         <v>19</v>
       </c>
-      <c r="W1" s="37" t="s">
+      <c r="W1" s="38" t="s">
         <v>20</v>
       </c>
-      <c r="X1" s="37" t="s">
+      <c r="X1" s="38" t="s">
         <v>21</v>
       </c>
-      <c r="Y1" s="37" t="s">
+      <c r="Y1" s="38" t="s">
         <v>22</v>
       </c>
-      <c r="Z1" s="37" t="s">
+      <c r="Z1" s="38" t="s">
         <v>23</v>
       </c>
-      <c r="AA1" s="37" t="s">
+      <c r="AA1" s="38" t="s">
         <v>24</v>
       </c>
-      <c r="AB1" s="37" t="s">
+      <c r="AB1" s="38" t="s">
         <v>25</v>
       </c>
-      <c r="AC1" s="37" t="s">
+      <c r="AC1" s="38" t="s">
         <v>26</v>
       </c>
-      <c r="AD1" s="37" t="s">
+      <c r="AD1" s="38" t="s">
         <v>27</v>
       </c>
-      <c r="AE1" s="37" t="s">
+      <c r="AE1" s="38" t="s">
         <v>28</v>
       </c>
-      <c r="AF1" s="37" t="s">
+      <c r="AF1" s="38" t="s">
         <v>29</v>
       </c>
-      <c r="AG1" s="37" t="s">
+      <c r="AG1" s="38" t="s">
         <v>30</v>
       </c>
-      <c r="AH1" s="37" t="s">
+      <c r="AH1" s="38" t="s">
         <v>31</v>
       </c>
-      <c r="AI1" s="37" t="s">
+      <c r="AI1" s="38" t="s">
         <v>32</v>
       </c>
-      <c r="AJ1" s="37" t="s">
+      <c r="AJ1" s="38" t="s">
         <v>33</v>
       </c>
-      <c r="AK1" s="37" t="s">
+      <c r="AK1" s="38" t="s">
         <v>34</v>
       </c>
-      <c r="AL1" s="37" t="s">
+      <c r="AL1" s="38" t="s">
         <v>35</v>
       </c>
-      <c r="AM1" s="37" t="s">
+      <c r="AM1" s="38" t="s">
         <v>36</v>
       </c>
-      <c r="AN1" s="37" t="s">
+      <c r="AN1" s="38" t="s">
         <v>37</v>
       </c>
-      <c r="AO1" s="37"/>
-      <c r="AP1" s="37"/>
-      <c r="AQ1" s="37"/>
-      <c r="AR1" s="37"/>
-      <c r="AS1" s="37"/>
-      <c r="AT1" s="37"/>
-      <c r="AU1" s="37" t="s">
+      <c r="AO1" s="38"/>
+      <c r="AP1" s="38"/>
+      <c r="AQ1" s="38"/>
+      <c r="AR1" s="38"/>
+      <c r="AS1" s="38"/>
+      <c r="AT1" s="38"/>
+      <c r="AU1" s="38" t="s">
         <v>38</v>
       </c>
-      <c r="AV1" s="37"/>
-      <c r="AW1" s="37"/>
-      <c r="AX1" s="37"/>
-      <c r="AY1" s="37"/>
-      <c r="AZ1" s="37"/>
-      <c r="BA1" s="37"/>
-      <c r="BB1" s="37" t="s">
+      <c r="AV1" s="38"/>
+      <c r="AW1" s="38"/>
+      <c r="AX1" s="38"/>
+      <c r="AY1" s="38"/>
+      <c r="AZ1" s="38"/>
+      <c r="BA1" s="38"/>
+      <c r="BB1" s="38" t="s">
         <v>38</v>
       </c>
-      <c r="BC1" s="37"/>
-      <c r="BD1" s="37"/>
-      <c r="BE1" s="37"/>
-      <c r="BF1" s="37"/>
-      <c r="BG1" s="37"/>
-      <c r="BH1" s="37"/>
-      <c r="BI1" s="37" t="s">
+      <c r="BC1" s="38"/>
+      <c r="BD1" s="38"/>
+      <c r="BE1" s="38"/>
+      <c r="BF1" s="38"/>
+      <c r="BG1" s="38"/>
+      <c r="BH1" s="38"/>
+      <c r="BI1" s="38" t="s">
         <v>38</v>
       </c>
-      <c r="BJ1" s="37"/>
-      <c r="BK1" s="37"/>
-      <c r="BL1" s="37"/>
-      <c r="BM1" s="37"/>
-      <c r="BN1" s="37"/>
-      <c r="BO1" s="37"/>
-      <c r="BP1" s="37" t="s">
+      <c r="BJ1" s="38"/>
+      <c r="BK1" s="38"/>
+      <c r="BL1" s="38"/>
+      <c r="BM1" s="38"/>
+      <c r="BN1" s="38"/>
+      <c r="BO1" s="38"/>
+      <c r="BP1" s="38" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:68" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A2" s="37"/>
-      <c r="B2" s="36"/>
-      <c r="C2" s="37"/>
-      <c r="D2" s="37"/>
-      <c r="E2" s="37"/>
-      <c r="F2" s="36"/>
-      <c r="G2" s="37"/>
-      <c r="H2" s="37"/>
-      <c r="I2" s="37"/>
-      <c r="J2" s="37"/>
-      <c r="K2" s="37"/>
-      <c r="L2" s="37"/>
-      <c r="M2" s="37"/>
-      <c r="N2" s="37"/>
-      <c r="O2" s="37"/>
-      <c r="P2" s="37"/>
-      <c r="Q2" s="37"/>
-      <c r="R2" s="37"/>
-      <c r="S2" s="37"/>
-      <c r="T2" s="37"/>
-      <c r="U2" s="37"/>
-      <c r="V2" s="37"/>
-      <c r="W2" s="37"/>
-      <c r="X2" s="37"/>
-      <c r="Y2" s="37"/>
-      <c r="Z2" s="37"/>
-      <c r="AA2" s="37"/>
-      <c r="AB2" s="37"/>
-      <c r="AC2" s="37"/>
-      <c r="AD2" s="37"/>
-      <c r="AE2" s="37"/>
-      <c r="AF2" s="37"/>
-      <c r="AG2" s="37"/>
-      <c r="AH2" s="37"/>
-      <c r="AI2" s="37"/>
-      <c r="AJ2" s="37"/>
-      <c r="AK2" s="37"/>
-      <c r="AL2" s="37"/>
-      <c r="AM2" s="37"/>
+      <c r="A2" s="38"/>
+      <c r="B2" s="39"/>
+      <c r="C2" s="38"/>
+      <c r="D2" s="38"/>
+      <c r="E2" s="38"/>
+      <c r="F2" s="39"/>
+      <c r="G2" s="38"/>
+      <c r="H2" s="38"/>
+      <c r="I2" s="38"/>
+      <c r="J2" s="38"/>
+      <c r="K2" s="38"/>
+      <c r="L2" s="38"/>
+      <c r="M2" s="38"/>
+      <c r="N2" s="38"/>
+      <c r="O2" s="38"/>
+      <c r="P2" s="38"/>
+      <c r="Q2" s="38"/>
+      <c r="R2" s="38"/>
+      <c r="S2" s="38"/>
+      <c r="T2" s="38"/>
+      <c r="U2" s="38"/>
+      <c r="V2" s="38"/>
+      <c r="W2" s="38"/>
+      <c r="X2" s="38"/>
+      <c r="Y2" s="38"/>
+      <c r="Z2" s="38"/>
+      <c r="AA2" s="38"/>
+      <c r="AB2" s="38"/>
+      <c r="AC2" s="38"/>
+      <c r="AD2" s="38"/>
+      <c r="AE2" s="38"/>
+      <c r="AF2" s="38"/>
+      <c r="AG2" s="38"/>
+      <c r="AH2" s="38"/>
+      <c r="AI2" s="38"/>
+      <c r="AJ2" s="38"/>
+      <c r="AK2" s="38"/>
+      <c r="AL2" s="38"/>
+      <c r="AM2" s="38"/>
       <c r="AN2" s="1" t="s">
         <v>42</v>
       </c>
@@ -1625,7 +1625,7 @@
       <c r="BO2" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="BP2" s="37"/>
+      <c r="BP2" s="38"/>
     </row>
     <row r="3" spans="1:68" x14ac:dyDescent="0.3">
       <c r="D3" s="2"/>
@@ -1652,30 +1652,12 @@
     </row>
   </sheetData>
   <mergeCells count="44">
-    <mergeCell ref="BP1:BP2"/>
-    <mergeCell ref="AG1:AG2"/>
-    <mergeCell ref="AH1:AH2"/>
-    <mergeCell ref="AI1:AI2"/>
-    <mergeCell ref="AJ1:AJ2"/>
-    <mergeCell ref="AK1:AK2"/>
-    <mergeCell ref="AL1:AL2"/>
-    <mergeCell ref="AM1:AM2"/>
-    <mergeCell ref="AN1:AT1"/>
-    <mergeCell ref="AU1:BA1"/>
-    <mergeCell ref="BB1:BH1"/>
-    <mergeCell ref="BI1:BO1"/>
-    <mergeCell ref="AF1:AF2"/>
-    <mergeCell ref="U1:U2"/>
-    <mergeCell ref="V1:V2"/>
-    <mergeCell ref="W1:W2"/>
-    <mergeCell ref="X1:X2"/>
-    <mergeCell ref="Y1:Y2"/>
-    <mergeCell ref="Z1:Z2"/>
-    <mergeCell ref="AA1:AA2"/>
-    <mergeCell ref="AB1:AB2"/>
-    <mergeCell ref="AC1:AC2"/>
-    <mergeCell ref="AD1:AD2"/>
-    <mergeCell ref="AE1:AE2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
     <mergeCell ref="T1:T2"/>
     <mergeCell ref="G1:G2"/>
     <mergeCell ref="I1:I2"/>
@@ -1690,12 +1672,30 @@
     <mergeCell ref="S1:S2"/>
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="J1:J2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="AF1:AF2"/>
+    <mergeCell ref="U1:U2"/>
+    <mergeCell ref="V1:V2"/>
+    <mergeCell ref="W1:W2"/>
+    <mergeCell ref="X1:X2"/>
+    <mergeCell ref="Y1:Y2"/>
+    <mergeCell ref="Z1:Z2"/>
+    <mergeCell ref="AA1:AA2"/>
+    <mergeCell ref="AB1:AB2"/>
+    <mergeCell ref="AC1:AC2"/>
+    <mergeCell ref="AD1:AD2"/>
+    <mergeCell ref="AE1:AE2"/>
+    <mergeCell ref="BP1:BP2"/>
+    <mergeCell ref="AG1:AG2"/>
+    <mergeCell ref="AH1:AH2"/>
+    <mergeCell ref="AI1:AI2"/>
+    <mergeCell ref="AJ1:AJ2"/>
+    <mergeCell ref="AK1:AK2"/>
+    <mergeCell ref="AL1:AL2"/>
+    <mergeCell ref="AM1:AM2"/>
+    <mergeCell ref="AN1:AT1"/>
+    <mergeCell ref="AU1:BA1"/>
+    <mergeCell ref="BB1:BH1"/>
+    <mergeCell ref="BI1:BO1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1728,10 +1728,10 @@
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="40" t="s">
+      <c r="C1" s="44" t="s">
         <v>49</v>
       </c>
-      <c r="D1" s="40"/>
+      <c r="D1" s="44"/>
       <c r="F1" s="5" t="s">
         <v>50</v>
       </c>
@@ -1743,10 +1743,10 @@
         <v>40</v>
       </c>
       <c r="L1" s="29"/>
-      <c r="M1" s="38" t="s">
+      <c r="M1" s="42" t="s">
         <v>41</v>
       </c>
-      <c r="N1" s="38"/>
+      <c r="N1" s="42"/>
       <c r="P1" s="9" t="s">
         <v>51</v>
       </c>
@@ -1766,7 +1766,7 @@
       <c r="AA1" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="AC1" s="44" t="s">
+      <c r="AC1" s="36" t="s">
         <v>11</v>
       </c>
     </row>
@@ -1774,7 +1774,7 @@
       <c r="A2" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="C2" s="39" t="s">
+      <c r="C2" s="43" t="s">
         <v>53</v>
       </c>
       <c r="D2" s="12" t="s">
@@ -1788,7 +1788,7 @@
       </c>
       <c r="J2" s="30"/>
       <c r="K2" s="34" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="L2" s="30"/>
       <c r="M2" s="6" t="s">
@@ -1815,45 +1815,45 @@
         <v>60</v>
       </c>
       <c r="AA2" s="18" t="s">
-        <v>61</v>
-      </c>
-      <c r="AC2" s="45" t="s">
         <v>243</v>
+      </c>
+      <c r="AC2" s="37" t="s">
+        <v>242</v>
       </c>
     </row>
     <row r="3" spans="1:29" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A3" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="C3" s="43"/>
+      <c r="D3" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="C3" s="39"/>
-      <c r="D3" s="12" t="s">
+      <c r="F3" s="13" t="s">
         <v>64</v>
       </c>
-      <c r="F3" s="13" t="s">
+      <c r="I3" s="14" t="s">
         <v>65</v>
-      </c>
-      <c r="I3" s="14" t="s">
-        <v>66</v>
       </c>
       <c r="J3" s="30"/>
       <c r="K3" s="34" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="L3" s="30"/>
-      <c r="M3" s="41" t="s">
+      <c r="M3" s="45" t="s">
         <v>56</v>
       </c>
       <c r="N3" s="28" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="P3" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="R3" s="15" t="s">
         <v>67</v>
       </c>
-      <c r="R3" s="15" t="s">
+      <c r="T3" s="16" t="s">
         <v>68</v>
-      </c>
-      <c r="T3" s="16" t="s">
-        <v>69</v>
       </c>
       <c r="U3" s="25"/>
       <c r="V3" s="19"/>
@@ -1861,852 +1861,852 @@
         <v>0.05</v>
       </c>
       <c r="Y3" s="16" t="s">
+        <v>69</v>
+      </c>
+      <c r="AA3" s="18" t="s">
         <v>70</v>
-      </c>
-      <c r="AA3" s="18" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="4" spans="1:29" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A4" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="C4" s="43"/>
+      <c r="D4" s="12" t="s">
         <v>73</v>
       </c>
-      <c r="C4" s="39"/>
-      <c r="D4" s="12" t="s">
+      <c r="F4" s="13" t="s">
         <v>74</v>
       </c>
-      <c r="F4" s="13" t="s">
+      <c r="I4" s="14" t="s">
         <v>75</v>
-      </c>
-      <c r="I4" s="14" t="s">
-        <v>76</v>
       </c>
       <c r="J4" s="30"/>
       <c r="K4" s="34" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="L4" s="30"/>
-      <c r="M4" s="41"/>
+      <c r="M4" s="45"/>
       <c r="N4" s="28" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="P4" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="R4" s="15" t="s">
         <v>77</v>
       </c>
-      <c r="R4" s="15" t="s">
+      <c r="T4" s="16" t="s">
         <v>78</v>
-      </c>
-      <c r="T4" s="16" t="s">
-        <v>79</v>
       </c>
       <c r="U4" s="25"/>
       <c r="W4" s="17">
         <v>0.12</v>
       </c>
       <c r="Y4" s="16" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="5" spans="1:29" ht="19.2" x14ac:dyDescent="0.3">
       <c r="A5" s="11" t="s">
+        <v>81</v>
+      </c>
+      <c r="C5" s="43"/>
+      <c r="D5" s="12" t="s">
         <v>82</v>
       </c>
-      <c r="C5" s="39"/>
-      <c r="D5" s="12" t="s">
+      <c r="F5" s="13" t="s">
         <v>83</v>
       </c>
-      <c r="F5" s="13" t="s">
+      <c r="I5" s="14" t="s">
         <v>84</v>
-      </c>
-      <c r="I5" s="14" t="s">
-        <v>85</v>
       </c>
       <c r="J5" s="30"/>
       <c r="K5" s="34" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="L5" s="30"/>
-      <c r="M5" s="41"/>
+      <c r="M5" s="45"/>
       <c r="N5" s="28" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="P5" s="16" t="s">
+        <v>85</v>
+      </c>
+      <c r="R5" s="15" t="s">
         <v>86</v>
       </c>
-      <c r="R5" s="15" t="s">
+      <c r="T5" s="16" t="s">
         <v>87</v>
-      </c>
-      <c r="T5" s="16" t="s">
-        <v>88</v>
       </c>
       <c r="U5" s="25"/>
       <c r="W5" s="17">
         <v>0.18</v>
       </c>
       <c r="Y5" s="16" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="6" spans="1:29" ht="19.2" x14ac:dyDescent="0.3">
       <c r="A6" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="C6" s="43"/>
+      <c r="D6" s="12" t="s">
         <v>91</v>
       </c>
-      <c r="C6" s="39"/>
-      <c r="D6" s="12" t="s">
+      <c r="F6" s="13" t="s">
         <v>92</v>
       </c>
-      <c r="F6" s="13" t="s">
+      <c r="I6" s="14" t="s">
         <v>93</v>
-      </c>
-      <c r="I6" s="14" t="s">
-        <v>94</v>
       </c>
       <c r="J6" s="30"/>
       <c r="K6" s="34" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="L6" s="30"/>
-      <c r="M6" s="42" t="s">
-        <v>66</v>
+      <c r="M6" s="40" t="s">
+        <v>65</v>
       </c>
       <c r="N6" s="28" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="P6" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="R6" s="15" t="s">
         <v>95</v>
       </c>
-      <c r="R6" s="15" t="s">
+      <c r="T6" s="16" t="s">
         <v>96</v>
-      </c>
-      <c r="T6" s="16" t="s">
-        <v>97</v>
       </c>
       <c r="U6" s="25"/>
       <c r="Y6" s="16" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="7" spans="1:29" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A7" s="11" t="s">
+        <v>99</v>
+      </c>
+      <c r="C7" s="43"/>
+      <c r="D7" s="12" t="s">
         <v>100</v>
       </c>
-      <c r="C7" s="39"/>
-      <c r="D7" s="12" t="s">
+      <c r="F7" s="13" t="s">
         <v>101</v>
       </c>
-      <c r="F7" s="13" t="s">
+      <c r="I7" s="14" t="s">
         <v>102</v>
-      </c>
-      <c r="I7" s="14" t="s">
-        <v>103</v>
       </c>
       <c r="J7" s="30"/>
       <c r="K7" s="34" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="L7" s="30"/>
-      <c r="M7" s="42"/>
+      <c r="M7" s="40"/>
       <c r="N7" s="28" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="P7" s="16" t="s">
+        <v>103</v>
+      </c>
+      <c r="R7" s="15" t="s">
         <v>104</v>
       </c>
-      <c r="R7" s="15" t="s">
+      <c r="T7" s="16" t="s">
         <v>105</v>
-      </c>
-      <c r="T7" s="16" t="s">
-        <v>106</v>
       </c>
       <c r="U7" s="25"/>
       <c r="Y7" s="16" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="8" spans="1:29" ht="30" x14ac:dyDescent="0.3">
       <c r="A8" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="C8" s="43"/>
+      <c r="D8" s="12" t="s">
         <v>109</v>
       </c>
-      <c r="C8" s="39"/>
-      <c r="D8" s="12" t="s">
+      <c r="I8" s="14" t="s">
         <v>110</v>
-      </c>
-      <c r="I8" s="14" t="s">
-        <v>111</v>
       </c>
       <c r="J8" s="30"/>
       <c r="K8" s="34" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="L8" s="30"/>
-      <c r="M8" s="42" t="s">
-        <v>76</v>
+      <c r="M8" s="40" t="s">
+        <v>75</v>
       </c>
       <c r="N8" s="28" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="P8" s="16" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="T8" s="16" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="U8" s="25"/>
       <c r="Y8" s="16" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="9" spans="1:29" ht="31.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="11" t="s">
+        <v>114</v>
+      </c>
+      <c r="C9" s="43"/>
+      <c r="D9" s="12" t="s">
         <v>115</v>
       </c>
-      <c r="C9" s="39"/>
-      <c r="D9" s="12" t="s">
+      <c r="I9" s="14" t="s">
         <v>116</v>
-      </c>
-      <c r="I9" s="14" t="s">
-        <v>117</v>
       </c>
       <c r="J9" s="30"/>
       <c r="K9" s="34" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="L9" s="30"/>
-      <c r="M9" s="42"/>
+      <c r="M9" s="40"/>
       <c r="N9" s="28" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="P9" s="16" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="T9" s="16" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="U9" s="25"/>
       <c r="Y9" s="16" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="10" spans="1:29" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A10" s="21"/>
-      <c r="C10" s="39" t="s">
-        <v>63</v>
+      <c r="C10" s="43" t="s">
+        <v>62</v>
       </c>
       <c r="D10" s="16" t="s">
+        <v>120</v>
+      </c>
+      <c r="I10" s="14" t="s">
         <v>121</v>
-      </c>
-      <c r="I10" s="14" t="s">
-        <v>122</v>
       </c>
       <c r="J10" s="30"/>
       <c r="L10" s="30"/>
-      <c r="M10" s="42" t="s">
-        <v>85</v>
+      <c r="M10" s="40" t="s">
+        <v>84</v>
       </c>
       <c r="N10" s="28" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="P10" s="16" t="s">
         <v>57</v>
       </c>
       <c r="T10" s="16" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="U10" s="25"/>
       <c r="Y10" s="16" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="11" spans="1:29" ht="31.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C11" s="43"/>
+      <c r="D11" s="16" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="11" spans="1:29" ht="31.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C11" s="39"/>
-      <c r="D11" s="16" t="s">
+      <c r="I11" s="14" t="s">
         <v>125</v>
-      </c>
-      <c r="I11" s="14" t="s">
-        <v>126</v>
       </c>
       <c r="J11" s="30"/>
       <c r="L11" s="30"/>
-      <c r="M11" s="42"/>
+      <c r="M11" s="40"/>
       <c r="N11" s="28" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="P11" s="16" t="s">
+        <v>126</v>
+      </c>
+      <c r="T11" s="16" t="s">
         <v>127</v>
-      </c>
-      <c r="T11" s="16" t="s">
-        <v>128</v>
       </c>
       <c r="U11" s="25"/>
       <c r="Y11" s="16" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="12" spans="1:29" ht="31.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C12" s="43"/>
+      <c r="D12" s="16" t="s">
         <v>129</v>
       </c>
-    </row>
-    <row r="12" spans="1:29" ht="31.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C12" s="39"/>
-      <c r="D12" s="16" t="s">
+      <c r="M12" s="40"/>
+      <c r="N12" s="28" t="s">
+        <v>236</v>
+      </c>
+      <c r="P12" s="16" t="s">
         <v>130</v>
       </c>
-      <c r="M12" s="42"/>
-      <c r="N12" s="28" t="s">
-        <v>237</v>
-      </c>
-      <c r="P12" s="16" t="s">
+      <c r="T12" s="16" t="s">
         <v>131</v>
-      </c>
-      <c r="T12" s="16" t="s">
-        <v>132</v>
       </c>
       <c r="U12" s="25"/>
       <c r="Y12" s="16" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="13" spans="1:29" ht="62.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C13" s="43"/>
+      <c r="D13" s="16" t="s">
         <v>133</v>
       </c>
-    </row>
-    <row r="13" spans="1:29" ht="62.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C13" s="39"/>
-      <c r="D13" s="16" t="s">
+      <c r="M13" s="40"/>
+      <c r="N13" s="28" t="s">
+        <v>229</v>
+      </c>
+      <c r="P13" s="16" t="s">
         <v>134</v>
       </c>
-      <c r="M13" s="42"/>
-      <c r="N13" s="28" t="s">
-        <v>230</v>
-      </c>
-      <c r="P13" s="16" t="s">
+      <c r="T13" s="16" t="s">
         <v>135</v>
-      </c>
-      <c r="T13" s="16" t="s">
-        <v>136</v>
       </c>
       <c r="U13" s="25"/>
       <c r="Y13" s="16" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="14" spans="1:29" ht="46.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C14" s="43"/>
+      <c r="D14" s="16" t="s">
         <v>137</v>
       </c>
-    </row>
-    <row r="14" spans="1:29" ht="46.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C14" s="39"/>
-      <c r="D14" s="16" t="s">
+      <c r="M14" s="40" t="s">
+        <v>93</v>
+      </c>
+      <c r="N14" s="28" t="s">
+        <v>229</v>
+      </c>
+      <c r="P14" s="16" t="s">
         <v>138</v>
       </c>
-      <c r="M14" s="42" t="s">
-        <v>94</v>
-      </c>
-      <c r="N14" s="28" t="s">
-        <v>230</v>
-      </c>
-      <c r="P14" s="16" t="s">
+      <c r="T14" s="16" t="s">
         <v>139</v>
-      </c>
-      <c r="T14" s="16" t="s">
-        <v>140</v>
       </c>
       <c r="U14" s="25"/>
       <c r="Y14" s="16" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="15" spans="1:29" ht="78" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C15" s="43"/>
+      <c r="D15" s="16" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="15" spans="1:29" ht="78" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C15" s="39"/>
-      <c r="D15" s="16" t="s">
+      <c r="M15" s="40"/>
+      <c r="N15" s="28" t="s">
+        <v>231</v>
+      </c>
+      <c r="P15" s="16" t="s">
         <v>142</v>
       </c>
-      <c r="M15" s="42"/>
-      <c r="N15" s="28" t="s">
-        <v>232</v>
-      </c>
-      <c r="P15" s="16" t="s">
+      <c r="T15" s="16" t="s">
         <v>143</v>
-      </c>
-      <c r="T15" s="16" t="s">
-        <v>144</v>
       </c>
       <c r="U15" s="25"/>
       <c r="Y15" s="16" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="16" spans="1:29" ht="62.4" x14ac:dyDescent="0.3">
+      <c r="C16" s="43" t="s">
+        <v>72</v>
+      </c>
+      <c r="D16" s="16" t="s">
         <v>145</v>
       </c>
-    </row>
-    <row r="16" spans="1:29" ht="62.4" x14ac:dyDescent="0.3">
-      <c r="C16" s="39" t="s">
-        <v>73</v>
-      </c>
-      <c r="D16" s="16" t="s">
+      <c r="M16" s="40"/>
+      <c r="N16" s="28" t="s">
+        <v>230</v>
+      </c>
+      <c r="P16" s="16" t="s">
         <v>146</v>
       </c>
-      <c r="M16" s="42"/>
-      <c r="N16" s="28" t="s">
-        <v>231</v>
-      </c>
-      <c r="P16" s="16" t="s">
+      <c r="T16" s="16" t="s">
         <v>147</v>
-      </c>
-      <c r="T16" s="16" t="s">
-        <v>148</v>
       </c>
       <c r="U16" s="25"/>
       <c r="Y16" s="16" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="17" spans="3:25" ht="62.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C17" s="43"/>
+      <c r="D17" s="16" t="s">
         <v>149</v>
       </c>
-    </row>
-    <row r="17" spans="3:25" ht="62.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C17" s="39"/>
-      <c r="D17" s="16" t="s">
+      <c r="M17" s="40" t="s">
+        <v>102</v>
+      </c>
+      <c r="N17" s="28" t="s">
+        <v>229</v>
+      </c>
+      <c r="P17" s="16" t="s">
         <v>150</v>
       </c>
-      <c r="M17" s="42" t="s">
-        <v>103</v>
-      </c>
-      <c r="N17" s="28" t="s">
-        <v>230</v>
-      </c>
-      <c r="P17" s="16" t="s">
+      <c r="T17" s="16" t="s">
         <v>151</v>
-      </c>
-      <c r="T17" s="16" t="s">
-        <v>152</v>
       </c>
       <c r="U17" s="25"/>
       <c r="Y17" s="16" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="18" spans="3:25" ht="31.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C18" s="43"/>
+      <c r="D18" s="16" t="s">
         <v>153</v>
       </c>
-    </row>
-    <row r="18" spans="3:25" ht="31.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C18" s="39"/>
-      <c r="D18" s="16" t="s">
+      <c r="M18" s="40"/>
+      <c r="N18" s="28" t="s">
+        <v>232</v>
+      </c>
+      <c r="P18" s="16" t="s">
         <v>154</v>
       </c>
-      <c r="M18" s="42"/>
-      <c r="N18" s="28" t="s">
-        <v>233</v>
-      </c>
-      <c r="P18" s="16" t="s">
+      <c r="T18" s="16" t="s">
         <v>155</v>
-      </c>
-      <c r="T18" s="16" t="s">
-        <v>156</v>
       </c>
       <c r="U18" s="25"/>
       <c r="Y18" s="16" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="19" spans="3:25" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="C19" s="43"/>
+      <c r="D19" s="16" t="s">
         <v>157</v>
       </c>
-    </row>
-    <row r="19" spans="3:25" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="C19" s="39"/>
-      <c r="D19" s="16" t="s">
+      <c r="M19" s="40" t="s">
+        <v>110</v>
+      </c>
+      <c r="N19" s="28" t="s">
+        <v>232</v>
+      </c>
+      <c r="P19" s="16" t="s">
         <v>158</v>
       </c>
-      <c r="M19" s="42" t="s">
-        <v>111</v>
-      </c>
-      <c r="N19" s="28" t="s">
-        <v>233</v>
-      </c>
-      <c r="P19" s="16" t="s">
+      <c r="T19" s="16" t="s">
         <v>159</v>
-      </c>
-      <c r="T19" s="16" t="s">
-        <v>160</v>
       </c>
       <c r="U19" s="25"/>
       <c r="Y19" s="16" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="20" spans="3:25" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="C20" s="43"/>
+      <c r="D20" s="16" t="s">
         <v>161</v>
       </c>
-    </row>
-    <row r="20" spans="3:25" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="C20" s="39"/>
-      <c r="D20" s="16" t="s">
+      <c r="M20" s="40"/>
+      <c r="N20" s="28" t="s">
+        <v>233</v>
+      </c>
+      <c r="P20" s="16" t="s">
         <v>162</v>
       </c>
-      <c r="M20" s="42"/>
-      <c r="N20" s="28" t="s">
-        <v>234</v>
-      </c>
-      <c r="P20" s="16" t="s">
+      <c r="T20" s="16" t="s">
         <v>163</v>
-      </c>
-      <c r="T20" s="16" t="s">
-        <v>164</v>
       </c>
       <c r="U20" s="25"/>
       <c r="Y20" s="16" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="21" spans="3:25" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="C21" s="43"/>
+      <c r="D21" s="16" t="s">
         <v>165</v>
       </c>
-    </row>
-    <row r="21" spans="3:25" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="C21" s="39"/>
-      <c r="D21" s="16" t="s">
+      <c r="M21" s="40"/>
+      <c r="N21" s="28" t="s">
+        <v>237</v>
+      </c>
+      <c r="P21" s="16" t="s">
         <v>166</v>
       </c>
-      <c r="M21" s="42"/>
-      <c r="N21" s="28" t="s">
-        <v>238</v>
-      </c>
-      <c r="P21" s="16" t="s">
+      <c r="T21" s="16" t="s">
         <v>167</v>
-      </c>
-      <c r="T21" s="16" t="s">
-        <v>168</v>
       </c>
       <c r="U21" s="25"/>
       <c r="Y21" s="16" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="22" spans="3:25" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="C22" s="43" t="s">
+        <v>81</v>
+      </c>
+      <c r="D22" s="16" t="s">
         <v>169</v>
       </c>
-    </row>
-    <row r="22" spans="3:25" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="C22" s="39" t="s">
-        <v>82</v>
-      </c>
-      <c r="D22" s="16" t="s">
+      <c r="M22" s="40" t="s">
+        <v>116</v>
+      </c>
+      <c r="N22" s="28" t="s">
+        <v>229</v>
+      </c>
+      <c r="P22" s="16" t="s">
         <v>170</v>
       </c>
-      <c r="M22" s="42" t="s">
-        <v>117</v>
-      </c>
-      <c r="N22" s="28" t="s">
-        <v>230</v>
-      </c>
-      <c r="P22" s="16" t="s">
+      <c r="Y22" s="16" t="s">
         <v>171</v>
       </c>
-      <c r="Y22" s="16" t="s">
+    </row>
+    <row r="23" spans="3:25" ht="46.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C23" s="43"/>
+      <c r="D23" s="16" t="s">
         <v>172</v>
       </c>
-    </row>
-    <row r="23" spans="3:25" ht="46.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C23" s="39"/>
-      <c r="D23" s="16" t="s">
+      <c r="M23" s="40"/>
+      <c r="N23" s="26" t="s">
+        <v>234</v>
+      </c>
+      <c r="P23" s="16" t="s">
         <v>173</v>
       </c>
-      <c r="M23" s="42"/>
-      <c r="N23" s="26" t="s">
-        <v>235</v>
-      </c>
-      <c r="P23" s="16" t="s">
+      <c r="Y23" s="16" t="s">
         <v>174</v>
       </c>
-      <c r="Y23" s="16" t="s">
+    </row>
+    <row r="24" spans="3:25" ht="31.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C24" s="43"/>
+      <c r="D24" s="16" t="s">
         <v>175</v>
       </c>
-    </row>
-    <row r="24" spans="3:25" ht="31.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C24" s="39"/>
-      <c r="D24" s="16" t="s">
+      <c r="M24" s="40"/>
+      <c r="N24" s="26" t="s">
+        <v>238</v>
+      </c>
+      <c r="P24" s="16" t="s">
         <v>176</v>
       </c>
-      <c r="M24" s="42"/>
-      <c r="N24" s="26" t="s">
+      <c r="Y24" s="16" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="25" spans="3:25" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="C25" s="43"/>
+      <c r="D25" s="16" t="s">
+        <v>178</v>
+      </c>
+      <c r="M25" s="40"/>
+      <c r="N25" s="26" t="s">
         <v>239</v>
       </c>
-      <c r="P24" s="16" t="s">
-        <v>177</v>
-      </c>
-      <c r="Y24" s="16" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="25" spans="3:25" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="C25" s="39"/>
-      <c r="D25" s="16" t="s">
+      <c r="P25" s="16" t="s">
         <v>179</v>
       </c>
-      <c r="M25" s="42"/>
-      <c r="N25" s="26" t="s">
+      <c r="Y25" s="16" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="26" spans="3:25" ht="62.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C26" s="43"/>
+      <c r="D26" s="16" t="s">
+        <v>181</v>
+      </c>
+      <c r="M26" s="41" t="s">
+        <v>121</v>
+      </c>
+      <c r="N26" s="26" t="s">
+        <v>229</v>
+      </c>
+      <c r="P26" s="16" t="s">
+        <v>182</v>
+      </c>
+      <c r="Y26" s="16" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="27" spans="3:25" ht="31.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C27" s="43" t="s">
+        <v>90</v>
+      </c>
+      <c r="D27" s="16" t="s">
+        <v>184</v>
+      </c>
+      <c r="M27" s="41"/>
+      <c r="N27" s="26" t="s">
         <v>240</v>
       </c>
-      <c r="P25" s="16" t="s">
-        <v>180</v>
-      </c>
-      <c r="Y25" s="16" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="26" spans="3:25" ht="62.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C26" s="39"/>
-      <c r="D26" s="16" t="s">
-        <v>182</v>
-      </c>
-      <c r="M26" s="43" t="s">
-        <v>122</v>
-      </c>
-      <c r="N26" s="26" t="s">
-        <v>230</v>
-      </c>
-      <c r="P26" s="16" t="s">
-        <v>183</v>
-      </c>
-      <c r="Y26" s="16" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="27" spans="3:25" ht="31.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C27" s="39" t="s">
-        <v>91</v>
-      </c>
-      <c r="D27" s="16" t="s">
+      <c r="P27" s="16" t="s">
         <v>185</v>
       </c>
-      <c r="M27" s="43"/>
-      <c r="N27" s="26" t="s">
+      <c r="Y27" s="16" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="28" spans="3:25" x14ac:dyDescent="0.3">
+      <c r="C28" s="43"/>
+      <c r="D28" s="16" t="s">
+        <v>187</v>
+      </c>
+      <c r="M28" s="41"/>
+      <c r="N28" s="26" t="s">
+        <v>234</v>
+      </c>
+      <c r="P28" s="16" t="s">
+        <v>188</v>
+      </c>
+      <c r="Y28" s="16" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="29" spans="3:25" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="C29" s="43"/>
+      <c r="D29" s="16" t="s">
+        <v>190</v>
+      </c>
+      <c r="M29" s="41" t="s">
+        <v>125</v>
+      </c>
+      <c r="N29" s="26" t="s">
+        <v>229</v>
+      </c>
+      <c r="P29" s="16" t="s">
+        <v>191</v>
+      </c>
+      <c r="Y29" s="16" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="30" spans="3:25" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="C30" s="43"/>
+      <c r="D30" s="16" t="s">
+        <v>193</v>
+      </c>
+      <c r="M30" s="41"/>
+      <c r="N30" s="26" t="s">
+        <v>232</v>
+      </c>
+      <c r="P30" s="16" t="s">
+        <v>194</v>
+      </c>
+      <c r="Y30" s="16" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="31" spans="3:25" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="C31" s="43"/>
+      <c r="D31" s="16" t="s">
+        <v>196</v>
+      </c>
+      <c r="M31" s="41"/>
+      <c r="N31" s="26" t="s">
         <v>241</v>
-      </c>
-      <c r="P27" s="16" t="s">
-        <v>186</v>
-      </c>
-      <c r="Y27" s="16" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="28" spans="3:25" x14ac:dyDescent="0.3">
-      <c r="C28" s="39"/>
-      <c r="D28" s="16" t="s">
-        <v>188</v>
-      </c>
-      <c r="M28" s="43"/>
-      <c r="N28" s="26" t="s">
-        <v>235</v>
-      </c>
-      <c r="P28" s="16" t="s">
-        <v>189</v>
-      </c>
-      <c r="Y28" s="16" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="29" spans="3:25" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="C29" s="39"/>
-      <c r="D29" s="16" t="s">
-        <v>191</v>
-      </c>
-      <c r="M29" s="43" t="s">
-        <v>126</v>
-      </c>
-      <c r="N29" s="26" t="s">
-        <v>230</v>
-      </c>
-      <c r="P29" s="16" t="s">
-        <v>192</v>
-      </c>
-      <c r="Y29" s="16" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="30" spans="3:25" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="C30" s="39"/>
-      <c r="D30" s="16" t="s">
-        <v>194</v>
-      </c>
-      <c r="M30" s="43"/>
-      <c r="N30" s="26" t="s">
-        <v>233</v>
-      </c>
-      <c r="P30" s="16" t="s">
-        <v>195</v>
-      </c>
-      <c r="Y30" s="16" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="31" spans="3:25" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="C31" s="39"/>
-      <c r="D31" s="16" t="s">
-        <v>197</v>
-      </c>
-      <c r="M31" s="43"/>
-      <c r="N31" s="26" t="s">
-        <v>242</v>
       </c>
       <c r="P31" s="16" t="s">
         <v>57</v>
       </c>
       <c r="Y31" s="16" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="32" spans="3:25" ht="31.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C32" s="43"/>
+      <c r="D32" s="16" t="s">
         <v>198</v>
       </c>
-    </row>
-    <row r="32" spans="3:25" ht="31.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C32" s="39"/>
-      <c r="D32" s="16" t="s">
+      <c r="P32" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="Y32" s="16" t="s">
         <v>199</v>
       </c>
-      <c r="P32" s="16" t="s">
-        <v>67</v>
-      </c>
-      <c r="Y32" s="16" t="s">
+    </row>
+    <row r="33" spans="3:25" x14ac:dyDescent="0.3">
+      <c r="C33" s="43"/>
+      <c r="D33" s="16" t="s">
         <v>200</v>
       </c>
-    </row>
-    <row r="33" spans="3:25" x14ac:dyDescent="0.3">
-      <c r="C33" s="39"/>
-      <c r="D33" s="16" t="s">
+      <c r="P33" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="Y33" s="16" t="s">
         <v>201</v>
       </c>
-      <c r="P33" s="16" t="s">
-        <v>77</v>
-      </c>
-      <c r="Y33" s="16" t="s">
+    </row>
+    <row r="34" spans="3:25" ht="31.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C34" s="43" t="s">
+        <v>99</v>
+      </c>
+      <c r="D34" s="16" t="s">
         <v>202</v>
       </c>
-    </row>
-    <row r="34" spans="3:25" ht="31.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C34" s="39" t="s">
-        <v>100</v>
-      </c>
-      <c r="D34" s="16" t="s">
+      <c r="P34" s="16" t="s">
+        <v>85</v>
+      </c>
+      <c r="Y34" s="16" t="s">
         <v>203</v>
       </c>
-      <c r="P34" s="16" t="s">
-        <v>86</v>
-      </c>
-      <c r="Y34" s="16" t="s">
+    </row>
+    <row r="35" spans="3:25" ht="31.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C35" s="43"/>
+      <c r="D35" s="16" t="s">
         <v>204</v>
       </c>
-    </row>
-    <row r="35" spans="3:25" ht="31.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C35" s="39"/>
-      <c r="D35" s="16" t="s">
+      <c r="P35" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="Y35" s="16" t="s">
         <v>205</v>
       </c>
-      <c r="P35" s="16" t="s">
-        <v>95</v>
-      </c>
-      <c r="Y35" s="16" t="s">
+    </row>
+    <row r="36" spans="3:25" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="C36" s="43"/>
+      <c r="D36" s="16" t="s">
         <v>206</v>
-      </c>
-    </row>
-    <row r="36" spans="3:25" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="C36" s="39"/>
-      <c r="D36" s="16" t="s">
-        <v>207</v>
       </c>
       <c r="P36" s="16" t="s">
         <v>57</v>
       </c>
       <c r="Y36" s="16" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="37" spans="3:25" ht="31.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C37" s="43"/>
+      <c r="D37" s="16" t="s">
         <v>208</v>
       </c>
-    </row>
-    <row r="37" spans="3:25" ht="31.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C37" s="39"/>
-      <c r="D37" s="16" t="s">
+      <c r="P37" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="Y37" s="16" t="s">
         <v>209</v>
       </c>
-      <c r="P37" s="16" t="s">
-        <v>67</v>
-      </c>
-      <c r="Y37" s="16" t="s">
+    </row>
+    <row r="38" spans="3:25" x14ac:dyDescent="0.3">
+      <c r="C38" s="43"/>
+      <c r="D38" s="16" t="s">
         <v>210</v>
       </c>
-    </row>
-    <row r="38" spans="3:25" x14ac:dyDescent="0.3">
-      <c r="C38" s="39"/>
-      <c r="D38" s="16" t="s">
+      <c r="P38" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="Y38" s="16" t="s">
         <v>211</v>
       </c>
-      <c r="P38" s="16" t="s">
-        <v>77</v>
-      </c>
-      <c r="Y38" s="16" t="s">
+    </row>
+    <row r="39" spans="3:25" ht="31.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C39" s="43"/>
+      <c r="D39" s="16" t="s">
         <v>212</v>
       </c>
-    </row>
-    <row r="39" spans="3:25" ht="31.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C39" s="39"/>
-      <c r="D39" s="16" t="s">
+      <c r="P39" s="16" t="s">
+        <v>85</v>
+      </c>
+      <c r="Y39" s="16" t="s">
         <v>213</v>
       </c>
-      <c r="P39" s="16" t="s">
-        <v>86</v>
-      </c>
-      <c r="Y39" s="16" t="s">
+    </row>
+    <row r="40" spans="3:25" ht="31.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C40" s="43" t="s">
+        <v>108</v>
+      </c>
+      <c r="D40" s="16" t="s">
         <v>214</v>
       </c>
-    </row>
-    <row r="40" spans="3:25" ht="31.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C40" s="39" t="s">
-        <v>109</v>
-      </c>
-      <c r="D40" s="16" t="s">
+      <c r="P40" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="Y40" s="16" t="s">
         <v>215</v>
       </c>
-      <c r="P40" s="16" t="s">
-        <v>95</v>
-      </c>
-      <c r="Y40" s="16" t="s">
+    </row>
+    <row r="41" spans="3:25" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="C41" s="43"/>
+      <c r="D41" s="16" t="s">
         <v>216</v>
-      </c>
-    </row>
-    <row r="41" spans="3:25" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="C41" s="39"/>
-      <c r="D41" s="16" t="s">
-        <v>217</v>
       </c>
       <c r="P41" s="16" t="s">
         <v>57</v>
       </c>
       <c r="Y41" s="16" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="42" spans="3:25" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="C42" s="43"/>
+      <c r="D42" s="16" t="s">
         <v>218</v>
       </c>
-    </row>
-    <row r="42" spans="3:25" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="C42" s="39"/>
-      <c r="D42" s="16" t="s">
+      <c r="P42" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="Y42" s="16" t="s">
         <v>219</v>
       </c>
-      <c r="P42" s="16" t="s">
-        <v>67</v>
-      </c>
-      <c r="Y42" s="16" t="s">
+    </row>
+    <row r="43" spans="3:25" x14ac:dyDescent="0.3">
+      <c r="C43" s="43"/>
+      <c r="D43" s="16" t="s">
         <v>220</v>
       </c>
-    </row>
-    <row r="43" spans="3:25" x14ac:dyDescent="0.3">
-      <c r="C43" s="39"/>
-      <c r="D43" s="16" t="s">
+      <c r="P43" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="Y43" s="16" t="s">
         <v>221</v>
       </c>
-      <c r="P43" s="16" t="s">
-        <v>77</v>
-      </c>
-      <c r="Y43" s="16" t="s">
+    </row>
+    <row r="44" spans="3:25" ht="31.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C44" s="43" t="s">
+        <v>114</v>
+      </c>
+      <c r="D44" s="16" t="s">
         <v>222</v>
       </c>
-    </row>
-    <row r="44" spans="3:25" ht="31.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C44" s="39" t="s">
-        <v>115</v>
-      </c>
-      <c r="D44" s="16" t="s">
+      <c r="P44" s="16" t="s">
+        <v>85</v>
+      </c>
+      <c r="Y44" s="16" t="s">
         <v>223</v>
       </c>
-      <c r="P44" s="16" t="s">
-        <v>86</v>
-      </c>
-      <c r="Y44" s="16" t="s">
+    </row>
+    <row r="45" spans="3:25" ht="31.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C45" s="43"/>
+      <c r="D45" s="16" t="s">
         <v>224</v>
       </c>
-    </row>
-    <row r="45" spans="3:25" ht="31.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C45" s="39"/>
-      <c r="D45" s="16" t="s">
+      <c r="P45" s="35" t="s">
+        <v>94</v>
+      </c>
+      <c r="Y45" s="16" t="s">
         <v>225</v>
       </c>
-      <c r="P45" s="35" t="s">
-        <v>95</v>
-      </c>
-      <c r="Y45" s="16" t="s">
+    </row>
+    <row r="46" spans="3:25" x14ac:dyDescent="0.3">
+      <c r="C46" s="43"/>
+      <c r="D46" s="16" t="s">
         <v>226</v>
       </c>
-    </row>
-    <row r="46" spans="3:25" x14ac:dyDescent="0.3">
-      <c r="C46" s="39"/>
-      <c r="D46" s="16" t="s">
+      <c r="Y46" s="16" t="s">
         <v>227</v>
       </c>
-      <c r="Y46" s="16" t="s">
+    </row>
+    <row r="47" spans="3:25" x14ac:dyDescent="0.3">
+      <c r="C47" s="43"/>
+      <c r="D47" s="16" t="s">
         <v>228</v>
-      </c>
-    </row>
-    <row r="47" spans="3:25" x14ac:dyDescent="0.3">
-      <c r="C47" s="39"/>
-      <c r="D47" s="16" t="s">
-        <v>229</v>
       </c>
     </row>
     <row r="48" spans="3:25" x14ac:dyDescent="0.3">
@@ -2756,11 +2756,6 @@
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="M19:M21"/>
-    <mergeCell ref="M22:M25"/>
-    <mergeCell ref="M26:M28"/>
-    <mergeCell ref="M29:M31"/>
-    <mergeCell ref="M1:N1"/>
     <mergeCell ref="C34:C39"/>
     <mergeCell ref="C40:C43"/>
     <mergeCell ref="C44:C47"/>
@@ -2770,6 +2765,11 @@
     <mergeCell ref="C16:C21"/>
     <mergeCell ref="C22:C26"/>
     <mergeCell ref="C27:C33"/>
+    <mergeCell ref="M19:M21"/>
+    <mergeCell ref="M22:M25"/>
+    <mergeCell ref="M26:M28"/>
+    <mergeCell ref="M29:M31"/>
+    <mergeCell ref="M1:N1"/>
     <mergeCell ref="M3:M5"/>
     <mergeCell ref="M6:M7"/>
     <mergeCell ref="M8:M9"/>
